--- a/artfynd/A 30953-2026 artfynd.xlsx
+++ b/artfynd/A 30953-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135953952</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135953947</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135953951</v>
       </c>
       <c r="B4" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135953948</v>
       </c>
       <c r="B5" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135953949</v>
       </c>
       <c r="B6" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135953950</v>
       </c>
       <c r="B7" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30953-2026 artfynd.xlsx
+++ b/artfynd/A 30953-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135953952</v>
       </c>
       <c r="B2" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135953951</v>
       </c>
       <c r="B4" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135953948</v>
       </c>
       <c r="B5" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135953949</v>
       </c>
       <c r="B6" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135953950</v>
       </c>
       <c r="B7" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30953-2026 artfynd.xlsx
+++ b/artfynd/A 30953-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135953952</v>
       </c>
       <c r="B2" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135953947</v>
       </c>
       <c r="B3" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135953951</v>
       </c>
       <c r="B4" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135953948</v>
       </c>
       <c r="B5" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135953949</v>
       </c>
       <c r="B6" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135953950</v>
       </c>
       <c r="B7" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30953-2026 artfynd.xlsx
+++ b/artfynd/A 30953-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135953952</v>
       </c>
       <c r="B2" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135953947</v>
       </c>
       <c r="B3" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135953951</v>
       </c>
       <c r="B4" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135953948</v>
       </c>
       <c r="B5" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135953949</v>
       </c>
       <c r="B6" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135953950</v>
       </c>
       <c r="B7" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30953-2026 artfynd.xlsx
+++ b/artfynd/A 30953-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135953952</v>
       </c>
       <c r="B2" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135953947</v>
       </c>
       <c r="B3" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135953951</v>
       </c>
       <c r="B4" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135953948</v>
       </c>
       <c r="B5" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135953949</v>
       </c>
       <c r="B6" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135953950</v>
       </c>
       <c r="B7" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30953-2026 artfynd.xlsx
+++ b/artfynd/A 30953-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135953952</v>
       </c>
       <c r="B2" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135953951</v>
       </c>
       <c r="B4" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135953948</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135953949</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135953950</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30953-2026 artfynd.xlsx
+++ b/artfynd/A 30953-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135953952</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135953947</v>
       </c>
       <c r="B3" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135953951</v>
       </c>
       <c r="B4" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135953948</v>
       </c>
       <c r="B5" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135953949</v>
       </c>
       <c r="B6" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135953950</v>
       </c>
       <c r="B7" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30953-2026 artfynd.xlsx
+++ b/artfynd/A 30953-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135953952</v>
       </c>
       <c r="B2" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135953947</v>
       </c>
       <c r="B3" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135953951</v>
       </c>
       <c r="B4" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135953948</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135953949</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135953950</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30953-2026 artfynd.xlsx
+++ b/artfynd/A 30953-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135953952</v>
       </c>
       <c r="B2" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135953951</v>
       </c>
       <c r="B4" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135953948</v>
       </c>
       <c r="B5" t="n">
-        <v>79496</v>
+        <v>79497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135953949</v>
       </c>
       <c r="B6" t="n">
-        <v>79496</v>
+        <v>79497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135953950</v>
       </c>
       <c r="B7" t="n">
-        <v>79496</v>
+        <v>79497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
